--- a/zy70609/test_data_检查结果.xlsx
+++ b/zy70609/test_data_检查结果.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60.00%</t>
+          <t>42.86%</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-17 16:44:48</t>
+          <t>2026-05-17 19:24:49</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>黑名单拦截</t>
+          <t>重复事件标记</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -550,7 +550,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>安全培训状态</t>
+          <t>黑名单拦截</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -560,10 +560,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>安全培训状态</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>人员档案校验</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>访客时段校验</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -578,22 +598,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -629,35 +651,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>是否重复</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>重复自事件ID</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>最终状态</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>最终消息</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>人员档案来源</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>闸机记录来源</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>访客申请来源</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>培训记录来源</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>黑名单来源</t>
         </is>
@@ -696,51 +728,57 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>所有规则校验通过</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>test_data.xlsx!人员档案!2行</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>test_data.xlsx!闸机记录!2行</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>test_data.xlsx!培训状态!2行</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>E006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17 08:05:00</t>
+          <t>2026-05-17 08:00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -755,56 +793,66 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>所有规则校验通过</t>
+          <t>E001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>test_data.xlsx!人员档案!3行</t>
+          <t>warn</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>test_data.xlsx!闸机记录!3行</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>该事件为重复事件，重复自事件[E001]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!人员档案!2行</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>test_data.xlsx!培训状态!3行</t>
+          <t>test_data.xlsx!闸机记录!7行</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!培训状态!2行</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E003</t>
+          <t>E002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-17 08:10:00</t>
+          <t>2026-05-17 08:05:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>西门闸机1</t>
+          <t>东门闸机1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -814,60 +862,62 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>block</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>人员[王五]在黑名单中，原因: 未佩戴安全帽累计3次; 人员[王五]安全培训未通过，当前状态: not_started</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>test_data.xlsx!人员档案!4行</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>test_data.xlsx!闸机记录!4行</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>所有规则校验通过</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!人员档案!3行</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>test_data.xlsx!培训状态!4行</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>test_data.xlsx!黑名单!2行</t>
-        </is>
-      </c>
+          <t>test_data.xlsx!闸机记录!3行</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!培训状态!3行</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E004</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>访客甲</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17 09:00:00</t>
+          <t>2026-05-17 08:10:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>东门闸机2</t>
+          <t>西门闸机1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -877,98 +927,236 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>所有规则校验通过</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>test_data.xlsx!人员档案!5行</t>
+          <t>block</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>test_data.xlsx!闸机记录!5行</t>
+          <t>人员[王五]在黑名单中，原因: 未佩戴安全帽累计3次; 人员[王五]安全培训未通过，当前状态: not_started</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>test_data.xlsx!访客申请!2行</t>
+          <t>test_data.xlsx!人员档案!4行</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>test_data.xlsx!培训状态!5行</t>
+          <t>test_data.xlsx!闸机记录!4行</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!培训状态!4行</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!黑名单!2行</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>访客甲</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-17 09:00:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>东门闸机2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>所有规则校验通过</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!人员档案!5行</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!闸机记录!5行</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!访客申请!2行</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!培训状态!5行</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>未知人员</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-17 10:00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>北门闸机</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>warn</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>人员[未知人员]无安全培训记录; 未找到人员[未知人员]的档案信息</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>test_data.xlsx!闸机记录!8行</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>E005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>V001</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>访客甲</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-05-17 18:00:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>东门闸机2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>exit</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>block</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>访客[访客甲]通行时间[2026-05-17 18:00:00]不在申请时段[2026-05-17 08:30:00~2026-05-17 17:30:00]内</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>test_data.xlsx!人员档案!5行</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>test_data.xlsx!闸机记录!6行</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>test_data.xlsx!访客申请!2行</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>test_data.xlsx!培训状态!5行</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -981,12 +1169,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -1107,59 +1295,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>E006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>安全培训状态</t>
+          <t>重复事件标记</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>warn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>人员[李四]安全培训状态有效</t>
+          <t>该事件为重复事件，重复自事件[E001]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{'passed_count': 1}</t>
+          <t>{'is_duplicate': True, 'duplicate_of': 'E001'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>E006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人员档案校验</t>
+          <t>安全培训状态</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1169,66 +1357,66 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>人员[李四]档案信息完整</t>
+          <t>人员[张三]安全培训状态有效</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'person_type': 'employee'}</t>
+          <t>{'passed_count': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E003</t>
+          <t>E006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>黑名单拦截</t>
+          <t>人员档案校验</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>人员[王五]在黑名单中，原因: 未佩戴安全帽累计3次</t>
+          <t>人员[张三]档案信息完整</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'blacklist_count': 1}</t>
+          <t>{'person_type': 'employee'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E003</t>
+          <t>E002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1238,34 +1426,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>人员[王五]安全培训未通过，当前状态: not_started</t>
+          <t>人员[李四]安全培训状态有效</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{'current_status': 'not_started'}</t>
+          <t>{'passed_count': 1}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E003</t>
+          <t>E002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1280,66 +1468,66 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>人员[王五]档案信息完整</t>
+          <t>人员[李四]档案信息完整</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{'person_type': 'contractor'}</t>
+          <t>{'person_type': 'employee'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E004</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>访客甲</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>访客时段校验</t>
+          <t>黑名单拦截</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>访客[访客甲]通行时间在有效申请时段内</t>
+          <t>人员[王五]在黑名单中，原因: 未佩戴安全帽累计3次</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>{'valid_applications': 1}</t>
+          <t>{'blacklist_count': 1}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E004</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>访客甲</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1349,34 +1537,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>block</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>人员[访客甲]安全培训状态有效</t>
+          <t>人员[王五]安全培训未通过，当前状态: not_started</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{'passed_count': 1}</t>
+          <t>{'current_status': 'not_started'}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E004</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>访客甲</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1391,19 +1579,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>人员[访客甲]档案信息完整</t>
+          <t>人员[王五]档案信息完整</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{'person_type': 'visitor'}</t>
+          <t>{'person_type': 'contractor'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E005</t>
+          <t>E004</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1423,24 +1611,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>访客[访客甲]通行时间[2026-05-17 18:00:00]不在申请时段[2026-05-17 08:30:00~2026-05-17 17:30:00]内</t>
+          <t>访客[访客甲]通行时间在有效申请时段内</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{'event_time': '2026-05-17T18:00:00', 'application_start': '2026-05-17T08:30:00', 'application_end': '2026-05-17T17:30:00'}</t>
+          <t>{'valid_applications': 1}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E005</t>
+          <t>E004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1477,35 +1665,220 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>访客甲</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>人员档案校验</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>人员[访客甲]档案信息完整</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'person_type': 'visitor'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E007</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>未知人员</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>安全培训状态</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>warn</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>人员[未知人员]无安全培训记录</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'has_training': False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>E007</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>未知人员</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>人员档案校验</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>warn</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>未找到人员[未知人员]的档案信息</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{'has_profile': False}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>E005</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>V001</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>访客甲</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>访客时段校验</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>访客[访客甲]通行时间[2026-05-17 18:00:00]不在申请时段[2026-05-17 08:30:00~2026-05-17 17:30:00]内</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{'event_time': '2026-05-17T18:00:00', 'application_start': '2026-05-17T08:30:00', 'application_end': '2026-05-17T17:30:00'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E005</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>访客甲</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>安全培训状态</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>人员[访客甲]安全培训状态有效</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{'passed_count': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E005</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>访客甲</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>人员档案校验</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>人员[访客甲]档案信息完整</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{'person_type': 'visitor'}</t>
         </is>
